--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14137" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14137" uniqueCount="1114">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1864,10 +1864,10 @@
     <t>Observation.component:gene-studied.value[x]</t>
   </si>
   <si>
-    <t>The HGNC gene symbol is to be used as display text and the HGNC gene ID used as the code. If no HGNC code issued for this gene yet, NCBI gene IDs SHALL be used.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/genomics-reporting/ValueSet/hgnc-vs</t>
+    <t>Untersuchtes Gen als HGNC-Gensymbol - strukturierte Entsprechung des Freitext-Gennamens nach 23.1 oBDS</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-marker-gene-hgnc</t>
   </si>
   <si>
     <t>Observation.component:gene-studied.dataAbsentReason</t>
@@ -3557,6 +3557,9 @@
   </si>
   <si>
     <t>HGNC-Format für Genfusionen GENESYMBOL1::GENESYMBOL2 und Readthrough-Transkripte GENESYMBOL1-GENESYMBOL2</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/genomics-reporting/ValueSet/hgnc-vs</t>
   </si>
   <si>
     <t>Observation.component:gene-fusion.dataAbsentReason</t>
@@ -16512,10 +16515,10 @@
         <v>230</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>546</v>
@@ -47096,7 +47099,7 @@
       </c>
       <c r="Y395" s="2"/>
       <c r="Z395" t="s" s="2">
-        <v>584</v>
+        <v>1096</v>
       </c>
       <c r="AA395" t="s" s="2">
         <v>78</v>
@@ -47137,7 +47140,7 @@
     </row>
     <row r="396" hidden="true">
       <c r="A396" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>547</v>
@@ -47247,7 +47250,7 @@
     </row>
     <row r="397" hidden="true">
       <c r="A397" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>551</v>
@@ -47357,7 +47360,7 @@
     </row>
     <row r="398" hidden="true">
       <c r="A398" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>552</v>
@@ -47467,13 +47470,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>528</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D399" t="s" s="2">
         <v>78</v>
@@ -47498,10 +47501,10 @@
         <v>468</v>
       </c>
       <c r="L399" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="N399" t="s" s="2">
         <v>531</v>
@@ -47579,7 +47582,7 @@
     </row>
     <row r="400" hidden="true">
       <c r="A400" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>535</v>
@@ -47685,7 +47688,7 @@
     </row>
     <row r="401" hidden="true">
       <c r="A401" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>536</v>
@@ -47793,7 +47796,7 @@
     </row>
     <row r="402" hidden="true">
       <c r="A402" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>537</v>
@@ -47903,7 +47906,7 @@
     </row>
     <row r="403" hidden="true">
       <c r="A403" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>538</v>
@@ -47951,7 +47954,7 @@
         <v>78</v>
       </c>
       <c r="S403" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="T403" t="s" s="2">
         <v>78</v>
@@ -48013,7 +48016,7 @@
     </row>
     <row r="404" hidden="true">
       <c r="A404" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>542</v>
@@ -48042,7 +48045,7 @@
         <v>861</v>
       </c>
       <c r="L404" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="M404" t="s" s="2">
         <v>545</v>
@@ -48123,7 +48126,7 @@
     </row>
     <row r="405" hidden="true">
       <c r="A405" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>547</v>
@@ -48233,7 +48236,7 @@
     </row>
     <row r="406" hidden="true">
       <c r="A406" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>551</v>
@@ -48343,7 +48346,7 @@
     </row>
     <row r="407" hidden="true">
       <c r="A407" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>552</v>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-genetische-variante.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
